--- a/outputs/monitor_xlsx/20260311.xlsx
+++ b/outputs/monitor_xlsx/20260311.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2370,7 +2370,7 @@
         <v>-106246</v>
       </c>
       <c r="N23" t="n">
-        <v>23.34</v>
+        <v>19.88</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2428,6 +2428,59 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5900</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="E25" t="n">
+        <v>750</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-135</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-436</v>
+      </c>
+      <c r="H25" t="n">
+        <v>31</v>
+      </c>
+      <c r="I25" t="n">
+        <v>369</v>
+      </c>
+      <c r="J25" t="n">
+        <v>31</v>
+      </c>
+      <c r="K25" t="n">
+        <v>256</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1343</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-8961</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260311.xlsx
+++ b/outputs/monitor_xlsx/20260311.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,220 +526,236 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>34114.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+1.79%</t>
-        </is>
-      </c>
+          <t>+4.10%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5157.8$</t>
+          <t>311.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.37%</t>
-        </is>
-      </c>
+          <t>+4.70%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>33985.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
+          <t>+3.88%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7914.56</t>
+          <t>4.21%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
+          <t>+1.79%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>5167.4$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-2.81%</t>
-        </is>
-      </c>
+          <t>-1.19%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>93.53$</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+12.08%</t>
-        </is>
-      </c>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>371.81億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-481.15億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-2405.74億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-149.78億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-2995.64億</t>
-        </is>
-      </c>
+          <t>7914.57</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>40.54億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>104.55億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>522.75億</t>
-        </is>
-      </c>
+          <t>24.23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-2.81%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>163.58%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>131.73%</t>
-        </is>
-      </c>
+          <t>87.25$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+4.55%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -749,12 +765,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>520.09億</t>
+          <t>371.81億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-513.66億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-2568.32億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -766,52 +803,135 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12693口</t>
-        </is>
-      </c>
+          <t>40.54億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13787口</t>
-        </is>
-      </c>
+          <t>103.83億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>519.16億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>520.09億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12693口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>13787口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-82.04億</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-7.31億</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-36.54億</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>-2.7億</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>-53.97億</t>
         </is>
@@ -860,7 +980,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-481.15億</t>
+          <t>-513.66億</t>
         </is>
       </c>
     </row>
@@ -872,7 +992,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2405.74億</t>
+          <t>-2568.32億</t>
         </is>
       </c>
     </row>
@@ -884,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-149.78億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -896,9 +1016,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-2995.64億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>104.55億</t>
+          <t>103.83億</t>
         </is>
       </c>
     </row>
@@ -920,7 +1044,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>522.75億</t>
+          <t>519.16億</t>
         </is>
       </c>
     </row>
@@ -994,7 +1118,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>131.73%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1039,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1135,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1203,13 +1320,13 @@
         <v>-15107</v>
       </c>
       <c r="H4" t="n">
-        <v>-528197</v>
+        <v>-392927</v>
       </c>
       <c r="I4" t="n">
         <v>3567</v>
       </c>
       <c r="J4" t="n">
-        <v>17763</v>
+        <v>13848</v>
       </c>
       <c r="K4" t="n">
         <v>33141</v>
@@ -1218,20 +1335,12 @@
         <v>12762</v>
       </c>
       <c r="M4" t="n">
-        <v>62231</v>
+        <v>50880</v>
       </c>
       <c r="N4" t="n">
         <v>-4425729</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1240,41 +1349,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>22</v>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>932</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3132</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-246</v>
       </c>
       <c r="H5" t="n">
-        <v>-504</v>
+        <v>-1394</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-157</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-405</v>
       </c>
       <c r="K5" t="n">
-        <v>761</v>
+        <v>85</v>
       </c>
       <c r="L5" t="n">
-        <v>9424</v>
+        <v>2769</v>
       </c>
       <c r="M5" t="n">
-        <v>49458</v>
+        <v>11229</v>
       </c>
       <c r="N5" t="n">
-        <v>-26299</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>-78829</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1283,12 +1404,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1297,47 +1418,39 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>932</v>
+        <v>1400</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2.19</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>3132</v>
+        <v>15114</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-246</v>
+        <v>-108</v>
       </c>
       <c r="H6" t="n">
-        <v>-1680</v>
+        <v>-1488</v>
       </c>
       <c r="I6" t="n">
-        <v>-157</v>
+        <v>270</v>
       </c>
       <c r="J6" t="n">
-        <v>-453</v>
+        <v>2049</v>
       </c>
       <c r="K6" t="n">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="L6" t="n">
-        <v>2769</v>
+        <v>5938</v>
       </c>
       <c r="M6" t="n">
-        <v>14021</v>
+        <v>23030</v>
       </c>
       <c r="N6" t="n">
-        <v>-78829</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>-648962</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1346,12 +1459,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1360,47 +1473,39 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1400</v>
+        <v>1940</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>8.529999999999999</v>
+        <v>4.86</v>
       </c>
       <c r="F7" t="n">
-        <v>15114</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>-108</v>
+        <v>39238</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>5027</v>
       </c>
       <c r="H7" t="n">
-        <v>-2609</v>
+        <v>-59488</v>
       </c>
       <c r="I7" t="n">
-        <v>270</v>
+        <v>-36</v>
       </c>
       <c r="J7" t="n">
-        <v>2342</v>
+        <v>5623</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>528</v>
       </c>
       <c r="L7" t="n">
-        <v>5938</v>
+        <v>24005</v>
       </c>
       <c r="M7" t="n">
-        <v>28880</v>
+        <v>96434</v>
       </c>
       <c r="N7" t="n">
-        <v>-648962</v>
-      </c>
-      <c r="O7" t="n">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>-6483129</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1409,12 +1514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1423,47 +1528,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1940</v>
+        <v>1485</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>4.86</v>
+        <v>3.48</v>
       </c>
       <c r="F8" t="n">
-        <v>39238</v>
+        <v>4197</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>5027</v>
+        <v>326</v>
       </c>
       <c r="H8" t="n">
-        <v>-86843</v>
+        <v>-475</v>
       </c>
       <c r="I8" t="n">
-        <v>-36</v>
+        <v>77</v>
       </c>
       <c r="J8" t="n">
-        <v>7090</v>
+        <v>650</v>
       </c>
       <c r="K8" t="n">
-        <v>528</v>
+        <v>163</v>
       </c>
       <c r="L8" t="n">
-        <v>24005</v>
+        <v>1842</v>
       </c>
       <c r="M8" t="n">
-        <v>118643</v>
+        <v>7223</v>
       </c>
       <c r="N8" t="n">
-        <v>-6483129</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140175</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1472,12 +1569,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1486,47 +1583,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>114</v>
+        <v>1495</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>8.06</v>
+        <v>9.93</v>
       </c>
       <c r="F9" t="n">
-        <v>182016</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>-9072</v>
+        <v>1745</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>239</v>
       </c>
       <c r="H9" t="n">
-        <v>25586</v>
+        <v>610</v>
       </c>
       <c r="I9" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>-7991</v>
+        <v>342</v>
       </c>
       <c r="K9" t="n">
-        <v>2270</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>135185</v>
+        <v>3114</v>
       </c>
       <c r="M9" t="n">
-        <v>618734</v>
+        <v>12689</v>
       </c>
       <c r="N9" t="n">
-        <v>-1114072</v>
-      </c>
-      <c r="O9" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106246</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1561,13 +1650,13 @@
         <v>-809</v>
       </c>
       <c r="H10" t="n">
-        <v>-1356</v>
+        <v>-1238</v>
       </c>
       <c r="I10" t="n">
         <v>168</v>
       </c>
       <c r="J10" t="n">
-        <v>1344</v>
+        <v>1279</v>
       </c>
       <c r="K10" t="n">
         <v>83</v>
@@ -1576,20 +1665,12 @@
         <v>1867</v>
       </c>
       <c r="M10" t="n">
-        <v>8869</v>
+        <v>7140</v>
       </c>
       <c r="N10" t="n">
         <v>-89489</v>
       </c>
-      <c r="O10" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1598,12 +1679,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1612,47 +1693,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3365</v>
+        <v>1810</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>9.970000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="F11" t="n">
-        <v>2203</v>
+        <v>932</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>834</v>
+        <v>112</v>
       </c>
       <c r="H11" t="n">
-        <v>-1221</v>
+        <v>-235</v>
       </c>
       <c r="I11" t="n">
-        <v>-15</v>
+        <v>-77</v>
       </c>
       <c r="J11" t="n">
-        <v>99</v>
+        <v>-269</v>
       </c>
       <c r="K11" t="n">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
-        <v>5933</v>
+        <v>4489</v>
       </c>
       <c r="M11" t="n">
-        <v>29930</v>
+        <v>18434</v>
       </c>
       <c r="N11" t="n">
-        <v>-19711</v>
-      </c>
-      <c r="O11" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19276</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1661,12 +1734,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1675,47 +1748,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1810</v>
+        <v>5900</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6.16</v>
+        <v>7.76</v>
       </c>
       <c r="F12" t="n">
-        <v>932</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>112</v>
+        <v>750</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-135</v>
       </c>
       <c r="H12" t="n">
-        <v>169</v>
+        <v>-301</v>
       </c>
       <c r="I12" t="n">
-        <v>-77</v>
+        <v>31</v>
       </c>
       <c r="J12" t="n">
-        <v>-264</v>
+        <v>338</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>4489</v>
+        <v>256</v>
       </c>
       <c r="M12" t="n">
-        <v>22755</v>
+        <v>1087</v>
       </c>
       <c r="N12" t="n">
-        <v>-19276</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-3.67</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8961</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1738,25 +1803,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1555</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4.71</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>5576</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-526</v>
       </c>
       <c r="H13" t="n">
-        <v>-3045</v>
+        <v>-2590</v>
       </c>
       <c r="I13" t="n">
         <v>-100</v>
       </c>
       <c r="J13" t="n">
-        <v>2655</v>
+        <v>2276</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
@@ -1765,20 +1830,12 @@
         <v>246</v>
       </c>
       <c r="M13" t="n">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1787,12 +1844,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1801,47 +1858,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>135.5</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.63</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>1490</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>72</v>
+        <v>3871</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-3</v>
       </c>
       <c r="H14" t="n">
-        <v>646</v>
+        <v>-141</v>
       </c>
       <c r="I14" t="n">
-        <v>-200</v>
+        <v>-95</v>
       </c>
       <c r="J14" t="n">
-        <v>-301</v>
+        <v>-1758</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="L14" t="n">
-        <v>-9</v>
+        <v>-67</v>
       </c>
       <c r="M14" t="n">
-        <v>-291</v>
+        <v>316</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1850,12 +1899,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1864,47 +1913,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>383.5</v>
+        <v>974</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>9.890000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>2873</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-3</v>
+        <v>-59</v>
       </c>
       <c r="H15" t="n">
-        <v>53</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-95</v>
+        <v>56</v>
       </c>
       <c r="J15" t="n">
-        <v>-2403</v>
+        <v>263</v>
       </c>
       <c r="K15" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="L15" t="n">
-        <v>-67</v>
+        <v>23</v>
       </c>
       <c r="M15" t="n">
-        <v>190</v>
+        <v>-273</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1913,12 +1951,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1927,560 +1965,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1265</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>10</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>311</v>
+        <v>904</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-49</v>
+        <v>-208</v>
       </c>
       <c r="H16" t="n">
-        <v>-748</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-4</v>
+        <v>612</v>
       </c>
       <c r="J16" t="n">
-        <v>-71</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>-144</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2587</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>197</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-1194</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>15</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4203</v>
-      </c>
-      <c r="M17" t="n">
-        <v>21119</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-11531</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1485</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4197</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>326</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-906</v>
-      </c>
-      <c r="I18" t="n">
-        <v>77</v>
-      </c>
-      <c r="J18" t="n">
-        <v>434</v>
-      </c>
-      <c r="K18" t="n">
-        <v>163</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1842</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9169</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-140175</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>770</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" t="n">
-        <v>517</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H19" t="n">
-        <v>819</v>
-      </c>
-      <c r="J19" t="n">
-        <v>27</v>
-      </c>
-      <c r="K19" t="n">
-        <v>23</v>
-      </c>
-      <c r="L19" t="n">
-        <v>50</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-791</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1085</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2356</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>382</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-596</v>
-      </c>
-      <c r="I20" t="n">
-        <v>26</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1531</v>
-      </c>
-      <c r="K20" t="n">
-        <v>89</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1938</v>
-      </c>
-      <c r="M20" t="n">
-        <v>10360</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-47605</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>962</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>826</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>-208</v>
-      </c>
-      <c r="G21" t="n">
-        <v>404</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>12</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>77</v>
-      </c>
-      <c r="L21" t="n">
-        <v>85</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>624</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>-59</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>263</v>
-      </c>
-      <c r="J22" t="n">
-        <v>82</v>
-      </c>
-      <c r="K22" t="n">
-        <v>23</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-250</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1495</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1745</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>239</v>
-      </c>
-      <c r="G23" t="n">
-        <v>849</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>347</v>
-      </c>
-      <c r="J23" t="n">
-        <v>33</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3114</v>
-      </c>
-      <c r="L23" t="n">
-        <v>15803</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-106246</v>
-      </c>
-      <c r="N23" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>253</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="E24" t="n">
-        <v>9176</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>-330</v>
-      </c>
-      <c r="G24" t="n">
-        <v>436</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" t="n">
-        <v>110</v>
-      </c>
-      <c r="J24" t="n">
-        <v>123</v>
-      </c>
-      <c r="K24" t="n">
-        <v>7365</v>
-      </c>
-      <c r="L24" t="n">
-        <v>35347</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-58883</v>
-      </c>
-      <c r="N24" t="n">
-        <v>19.13</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5900</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="E25" t="n">
-        <v>750</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>-135</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-436</v>
-      </c>
-      <c r="H25" t="n">
-        <v>31</v>
-      </c>
-      <c r="I25" t="n">
-        <v>369</v>
-      </c>
-      <c r="J25" t="n">
-        <v>31</v>
-      </c>
-      <c r="K25" t="n">
-        <v>256</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1343</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-8961</v>
-      </c>
-      <c r="N25" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260311.xlsx
+++ b/outputs/monitor_xlsx/20260311.xlsx
@@ -544,10 +544,6 @@
           <t>+4.10%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+4.70%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+3.88%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+1.79%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-1.19%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.10%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+0.63%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-2.81%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+4.55%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>371.81億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-513.66億</t>
@@ -811,7 +774,6 @@
           <t>40.54億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>103.83億</t>
@@ -822,8 +784,6 @@
           <t>519.16億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>520.09億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>12693口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>13787口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-82.04億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-7.31億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1942,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>323</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6044</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-1407</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-2033</v>
+      </c>
+      <c r="H17" t="n">
+        <v>573</v>
+      </c>
+      <c r="I17" t="n">
+        <v>424</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7550</v>
+      </c>
+      <c r="L17" t="n">
+        <v>34382</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22097</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11.89</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260311.xlsx
+++ b/outputs/monitor_xlsx/20260311.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>78.2</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3.99</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>151798</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-15107</v>
       </c>
       <c r="H4" t="n">
-        <v>-392927</v>
+        <v>-408035</v>
       </c>
       <c r="I4" t="n">
         <v>3567</v>
       </c>
       <c r="J4" t="n">
-        <v>13848</v>
+        <v>17415</v>
       </c>
       <c r="K4" t="n">
         <v>33141</v>
@@ -1279,11 +1278,14 @@
         <v>12762</v>
       </c>
       <c r="M4" t="n">
-        <v>50880</v>
+        <v>63642</v>
       </c>
       <c r="N4" t="n">
         <v>-4425729</v>
       </c>
+      <c r="O4" t="n">
+        <v>2.7</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>932</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>2.19</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>3132</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>-246</v>
       </c>
       <c r="H5" t="n">
-        <v>-1394</v>
+        <v>-1640</v>
       </c>
       <c r="I5" t="n">
         <v>-157</v>
       </c>
       <c r="J5" t="n">
-        <v>-405</v>
+        <v>-562</v>
       </c>
       <c r="K5" t="n">
         <v>85</v>
@@ -1334,11 +1336,14 @@
         <v>2769</v>
       </c>
       <c r="M5" t="n">
-        <v>11229</v>
+        <v>13998</v>
       </c>
       <c r="N5" t="n">
         <v>-78829</v>
       </c>
+      <c r="O5" t="n">
+        <v>-2.82</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1400</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>15114</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>-108</v>
       </c>
       <c r="H6" t="n">
-        <v>-1488</v>
+        <v>-1596</v>
       </c>
       <c r="I6" t="n">
         <v>270</v>
       </c>
       <c r="J6" t="n">
-        <v>2049</v>
+        <v>2319</v>
       </c>
       <c r="K6" t="n">
         <v>319</v>
@@ -1389,11 +1394,14 @@
         <v>5938</v>
       </c>
       <c r="M6" t="n">
-        <v>23030</v>
+        <v>28968</v>
       </c>
       <c r="N6" t="n">
         <v>-648962</v>
       </c>
+      <c r="O6" t="n">
+        <v>9.06</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1940</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4.86</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>39238</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>5027</v>
       </c>
       <c r="H7" t="n">
-        <v>-59488</v>
+        <v>-54461</v>
       </c>
       <c r="I7" t="n">
         <v>-36</v>
       </c>
       <c r="J7" t="n">
-        <v>5623</v>
+        <v>5587</v>
       </c>
       <c r="K7" t="n">
         <v>528</v>
@@ -1444,11 +1452,14 @@
         <v>24005</v>
       </c>
       <c r="M7" t="n">
-        <v>96434</v>
+        <v>120439</v>
       </c>
       <c r="N7" t="n">
         <v>-6483129</v>
       </c>
+      <c r="O7" t="n">
+        <v>3.34</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1485</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>3.48</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>4197</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>326</v>
       </c>
       <c r="H8" t="n">
-        <v>-475</v>
+        <v>-149</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
       </c>
       <c r="J8" t="n">
-        <v>650</v>
+        <v>727</v>
       </c>
       <c r="K8" t="n">
         <v>163</v>
@@ -1499,11 +1510,14 @@
         <v>1842</v>
       </c>
       <c r="M8" t="n">
-        <v>7223</v>
+        <v>9065</v>
       </c>
       <c r="N8" t="n">
         <v>-140175</v>
       </c>
+      <c r="O8" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1495</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>9.93</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>1745</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>239</v>
       </c>
       <c r="H9" t="n">
-        <v>610</v>
+        <v>849</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K9" t="n">
         <v>33</v>
@@ -1554,11 +1568,14 @@
         <v>3114</v>
       </c>
       <c r="M9" t="n">
-        <v>12689</v>
+        <v>15803</v>
       </c>
       <c r="N9" t="n">
         <v>-106246</v>
       </c>
+      <c r="O9" t="n">
+        <v>23.34</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2450</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>3.16</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>4829</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>-809</v>
       </c>
       <c r="H10" t="n">
-        <v>-1238</v>
+        <v>-2048</v>
       </c>
       <c r="I10" t="n">
         <v>168</v>
       </c>
       <c r="J10" t="n">
-        <v>1279</v>
+        <v>1447</v>
       </c>
       <c r="K10" t="n">
         <v>83</v>
@@ -1609,11 +1626,14 @@
         <v>1867</v>
       </c>
       <c r="M10" t="n">
-        <v>7140</v>
+        <v>9007</v>
       </c>
       <c r="N10" t="n">
         <v>-89489</v>
       </c>
+      <c r="O10" t="n">
+        <v>11.63</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>1810</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>6.16</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>932</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>112</v>
       </c>
       <c r="H11" t="n">
-        <v>-235</v>
+        <v>-123</v>
       </c>
       <c r="I11" t="n">
         <v>-77</v>
       </c>
       <c r="J11" t="n">
-        <v>-269</v>
+        <v>-346</v>
       </c>
       <c r="K11" t="n">
         <v>23</v>
@@ -1664,11 +1684,14 @@
         <v>4489</v>
       </c>
       <c r="M11" t="n">
-        <v>18434</v>
+        <v>22923</v>
       </c>
       <c r="N11" t="n">
         <v>-19276</v>
       </c>
+      <c r="O11" t="n">
+        <v>-6.74</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>5900</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>7.76</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>750</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>-135</v>
       </c>
       <c r="H12" t="n">
-        <v>-301</v>
+        <v>-436</v>
       </c>
       <c r="I12" t="n">
         <v>31</v>
       </c>
       <c r="J12" t="n">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="K12" t="n">
         <v>31</v>
@@ -1719,11 +1742,14 @@
         <v>256</v>
       </c>
       <c r="M12" t="n">
-        <v>1087</v>
+        <v>1343</v>
       </c>
       <c r="N12" t="n">
         <v>-8961</v>
       </c>
+      <c r="O12" t="n">
+        <v>22.13</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-526</v>
       </c>
       <c r="H13" t="n">
-        <v>-2590</v>
+        <v>-3116</v>
       </c>
       <c r="I13" t="n">
         <v>-100</v>
       </c>
       <c r="J13" t="n">
-        <v>2276</v>
+        <v>2176</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
@@ -1774,11 +1800,14 @@
         <v>246</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>296</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-3</v>
       </c>
       <c r="H14" t="n">
-        <v>-141</v>
+        <v>-144</v>
       </c>
       <c r="I14" t="n">
         <v>-95</v>
       </c>
       <c r="J14" t="n">
-        <v>-1758</v>
+        <v>-1853</v>
       </c>
       <c r="K14" t="n">
         <v>42</v>
@@ -1829,11 +1858,14 @@
         <v>-67</v>
       </c>
       <c r="M14" t="n">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1856,20 +1888,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-59</v>
       </c>
       <c r="H15" t="n">
-        <v>56</v>
+        <v>-3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>263</v>
@@ -1881,11 +1916,14 @@
         <v>23</v>
       </c>
       <c r="M15" t="n">
-        <v>-273</v>
+        <v>-250</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1946,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-208</v>
       </c>
       <c r="H16" t="n">
-        <v>612</v>
+        <v>404</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>12</v>
@@ -1933,11 +1974,14 @@
         <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>323</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>6044</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>-1407</v>
       </c>
-      <c r="G17" t="n">
-        <v>-2033</v>
-      </c>
       <c r="H17" t="n">
+        <v>-2372</v>
+      </c>
+      <c r="I17" t="n">
         <v>573</v>
       </c>
-      <c r="I17" t="n">
-        <v>424</v>
-      </c>
       <c r="J17" t="n">
+        <v>559</v>
+      </c>
+      <c r="K17" t="n">
         <v>10</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>7550</v>
       </c>
-      <c r="L17" t="n">
-        <v>34382</v>
-      </c>
       <c r="M17" t="n">
+        <v>34724</v>
+      </c>
+      <c r="N17" t="n">
         <v>-22097</v>
       </c>
-      <c r="N17" t="n">
-        <v>11.89</v>
+      <c r="O17" t="n">
+        <v>20.79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260311.xlsx
+++ b/outputs/monitor_xlsx/20260311.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>20.79</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6109</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-948</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-6325</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-97</v>
+      </c>
+      <c r="J18" t="n">
+        <v>215</v>
+      </c>
+      <c r="K18" t="n">
+        <v>98</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5799</v>
+      </c>
+      <c r="M18" t="n">
+        <v>28920</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400933</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>466</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15139</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1806</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-88</v>
+      </c>
+      <c r="I19" t="n">
+        <v>322</v>
+      </c>
+      <c r="J19" t="n">
+        <v>273</v>
+      </c>
+      <c r="K19" t="n">
+        <v>214</v>
+      </c>
+      <c r="L19" t="n">
+        <v>36844</v>
+      </c>
+      <c r="M19" t="n">
+        <v>190022</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392452</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>470.5</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1732</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I20" t="n">
+        <v>66</v>
+      </c>
+      <c r="J20" t="n">
+        <v>686</v>
+      </c>
+      <c r="K20" t="n">
+        <v>170</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8730</v>
+      </c>
+      <c r="M20" t="n">
+        <v>47017</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161541</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
